--- a/317 Newell St/Results/Excels/Performance_KPIs.xlsx
+++ b/317 Newell St/Results/Excels/Performance_KPIs.xlsx
@@ -424,10 +424,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>-8.201936737888872</v>
+        <v>-8.933769168780863</v>
       </c>
       <c r="C2">
-        <v>-3597.574501656507</v>
+        <v>-3918.574501656507</v>
       </c>
       <c r="D2">
         <v>43862.5</v>
@@ -438,10 +438,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>-2.480156882104665</v>
+        <v>-3.585258050528725</v>
       </c>
       <c r="C3">
-        <v>-1087.858812413159</v>
+        <v>-1572.583812413162</v>
       </c>
       <c r="D3">
         <v>43862.5</v>
@@ -452,10 +452,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>-2.692992376547527</v>
+        <v>-3.811699985552947</v>
       </c>
       <c r="C4">
-        <v>-1181.213781163159</v>
+        <v>-1671.906906163161</v>
       </c>
       <c r="D4">
         <v>43862.5</v>
@@ -466,10 +466,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>-2.585761088550001</v>
+        <v>-3.732436387780553</v>
       </c>
       <c r="C5">
-        <v>-1134.179457465244</v>
+        <v>-1637.139910590245</v>
       </c>
       <c r="D5">
         <v>43862.5</v>
@@ -480,10 +480,10 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>-2.468378947107166</v>
+        <v>-3.64372112881848</v>
       </c>
       <c r="C6">
-        <v>-1082.692715674881</v>
+        <v>-1598.227180128006</v>
       </c>
       <c r="D6">
         <v>43862.5</v>
@@ -494,10 +494,10 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>-2.34062167669367</v>
+        <v>-3.545347412947761</v>
       </c>
       <c r="C7">
-        <v>-1026.655182939761</v>
+        <v>-1555.078009004212</v>
       </c>
       <c r="D7">
         <v>43862.5</v>
@@ -508,10 +508,10 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>-2.202260574728433</v>
+        <v>-3.437104454388878</v>
       </c>
       <c r="C8">
-        <v>-965.9665445902588</v>
+        <v>-1507.599941306322</v>
       </c>
       <c r="D8">
         <v>43862.5</v>
@@ -522,10 +522,10 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>-2.0530624480916</v>
+        <v>-3.318777424743564</v>
       </c>
       <c r="C9">
-        <v>-900.5245162941778</v>
+        <v>-1455.698747928146</v>
       </c>
       <c r="D9">
         <v>43862.5</v>
@@ -536,10 +536,10 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>-1.892789549942089</v>
+        <v>-3.190147401010347</v>
       </c>
       <c r="C10">
-        <v>-830.2248163433489</v>
+        <v>-1399.278403768163</v>
       </c>
       <c r="D10">
         <v>43862.5</v>
@@ -550,10 +550,10 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>-1.721199516918767</v>
+        <v>-3.050991314263727</v>
       </c>
       <c r="C11">
-        <v>-754.9611381084942</v>
+        <v>-1338.241065218927</v>
       </c>
       <c r="D11">
         <v>43862.5</v>
@@ -564,10 +564,10 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>-1.53804530681359</v>
+        <v>-2.90108189909218</v>
       </c>
       <c r="C12">
-        <v>-674.6251227011106</v>
+        <v>-1272.487047989307</v>
       </c>
       <c r="D12">
         <v>43862.5</v>
@@ -578,10 +578,10 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>-1.343075136809851</v>
+        <v>-2.740187643895406</v>
       </c>
       <c r="C13">
-        <v>-589.1063318832207</v>
+        <v>-1201.914805303622</v>
       </c>
       <c r="D13">
         <v>43862.5</v>
@@ -592,10 +592,10 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>-1.136032422384842</v>
+        <v>-2.568072742147527</v>
       </c>
       <c r="C14">
-        <v>-498.2922212685514</v>
+        <v>-1126.420906524459</v>
       </c>
       <c r="D14">
         <v>43862.5</v>
@@ -606,10 +606,10 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>-0.9166557169817396</v>
+        <v>-2.384497044738504</v>
       </c>
       <c r="C15">
-        <v>-402.0681138611155</v>
+        <v>-1045.900016248426</v>
       </c>
       <c r="D15">
         <v>43862.5</v>
@@ -620,10 +620,10 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>-0.68467865256201</v>
+        <v>-2.189216013512687</v>
       </c>
       <c r="C16">
-        <v>-300.3171739800116</v>
+        <v>-960.2448739270021</v>
       </c>
       <c r="D16">
         <v>43862.5</v>
@@ -634,10 +634,10 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>-0.4398298811555597</v>
+        <v>-1.981980676130005</v>
       </c>
       <c r="C17">
-        <v>-192.9203816218574</v>
+        <v>-869.3462740675234</v>
       </c>
       <c r="D17">
         <v>43862.5</v>
@@ -648,10 +648,10 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>-0.1818330175332416</v>
+        <v>-1.762537582382058</v>
       </c>
       <c r="C18">
-        <v>-79.75650731551809</v>
+        <v>-773.0930470723304</v>
       </c>
       <c r="D18">
         <v>43862.5</v>
@@ -662,10 +662,10 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0.08959341686695485</v>
+        <v>-1.530628762103072</v>
       </c>
       <c r="C19">
-        <v>39.29791247326807</v>
+        <v>-671.3720407774598</v>
       </c>
       <c r="D19">
         <v>43862.5</v>
@@ -676,10 +676,10 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>0.3747360486214085</v>
+        <v>-1.285991684822857</v>
       </c>
       <c r="C20">
-        <v>164.3685993265653</v>
+        <v>-564.0681027554256</v>
       </c>
       <c r="D20">
         <v>43862.5</v>
@@ -690,10 +690,10 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0.6738867054631527</v>
+        <v>-1.028359221317225</v>
       </c>
       <c r="C21">
-        <v>295.5835561837753</v>
+        <v>-451.0640634502677</v>
       </c>
       <c r="D21">
         <v>43862.5</v>
@@ -704,10 +704,10 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0.9873424677305062</v>
+        <v>-0.7574596072193851</v>
       </c>
       <c r="C22">
-        <v>433.0730899082932</v>
+        <v>-332.2407202166028</v>
       </c>
       <c r="D22">
         <v>43862.5</v>
@@ -718,10 +718,10 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>1.315405717958728</v>
+        <v>-0.4730164088649196</v>
       </c>
       <c r="C23">
-        <v>576.9698330396471</v>
+        <v>-207.4768223383754</v>
       </c>
       <c r="D23">
         <v>43862.5</v>
@@ -732,10 +732,10 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>1.658384188442401</v>
+        <v>-0.1747484915518336</v>
       </c>
       <c r="C24">
-        <v>727.4087646555481</v>
+        <v>-76.64905710692301</v>
       </c>
       <c r="D24">
         <v>43862.5</v>
@@ -746,10 +746,10 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>2.016591006587315</v>
+        <v>0.137630009593231</v>
       </c>
       <c r="C25">
-        <v>884.5272302643612</v>
+        <v>60.36796295783097</v>
       </c>
       <c r="D25">
         <v>43862.5</v>
@@ -760,10 +760,10 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>2.390344737860391</v>
+        <v>0.4644097159414627</v>
       </c>
       <c r="C26">
-        <v>1048.464960644014</v>
+        <v>203.7017116548241</v>
       </c>
       <c r="D26">
         <v>43862.5</v>
@@ -774,10 +774,10 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>2.779969426136218</v>
+        <v>0.8058860286693179</v>
       </c>
       <c r="C27">
-        <v>1219.364089538999</v>
+        <v>353.4817593250796</v>
       </c>
       <c r="D27">
         <v>43862.5</v>
@@ -788,10 +788,10 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>3.185794631228124</v>
+        <v>1.162359148824533</v>
       </c>
       <c r="C28">
-        <v>1397.369170122436</v>
+        <v>509.8397816531606</v>
       </c>
       <c r="D28">
         <v>43862.5</v>
@@ -802,10 +802,10 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>3.608155463380283</v>
+        <v>1.534134093916612</v>
       </c>
       <c r="C29">
-        <v>1582.627190125177</v>
+        <v>672.909566944174</v>
       </c>
       <c r="D29">
         <v>43862.5</v>
@@ -816,10 +816,10 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>4.047392614485933</v>
+        <v>1.921520710785678</v>
       </c>
       <c r="C30">
-        <v>1775.287585528892</v>
+        <v>842.827021768368</v>
       </c>
       <c r="D30">
         <v>43862.5</v>
@@ -830,10 +830,10 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>4.503852385784318</v>
+        <v>2.324833684491544</v>
       </c>
       <c r="C31">
-        <v>1975.502252714647</v>
+        <v>1019.730174860103</v>
       </c>
       <c r="D31">
         <v>43862.5</v>
@@ -844,10 +844,10 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>0.3659616902357496</v>
+        <v>0.18400697179786</v>
       </c>
       <c r="C32">
-        <v>160.5199463796557</v>
+        <v>80.71005800483636</v>
       </c>
       <c r="D32">
         <v>43862.5</v>
@@ -897,10 +897,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>-3571.993395746492</v>
+        <v>-3937.993395746492</v>
       </c>
       <c r="C2">
-        <v>-3571.993395746492</v>
+        <v>-3937.993395746492</v>
       </c>
       <c r="D2">
         <v>145000</v>
@@ -912,7 +912,7 @@
         <v>11600</v>
       </c>
       <c r="G2">
-        <v>22156.35913539171</v>
+        <v>21790.35913539171</v>
       </c>
       <c r="H2">
         <v>-100</v>
@@ -926,10 +926,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>-4792.655124826318</v>
+        <v>-5638.355124826321</v>
       </c>
       <c r="C3">
-        <v>-1220.661729079825</v>
+        <v>-1700.361729079829</v>
       </c>
       <c r="D3">
         <v>147900</v>
@@ -941,10 +941,10 @@
         <v>11832</v>
       </c>
       <c r="G3">
-        <v>24761.44194880568</v>
+        <v>23915.74194880568</v>
       </c>
       <c r="H3">
-        <v>-43.5475817639084</v>
+        <v>-45.47565243931451</v>
       </c>
       <c r="I3">
         <v>43862.5</v>
@@ -955,10 +955,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>-5970.282728906143</v>
+        <v>-7307.675228906149</v>
       </c>
       <c r="C4">
-        <v>-1177.627604079826</v>
+        <v>-1669.320104079828</v>
       </c>
       <c r="D4">
         <v>150858</v>
@@ -970,10 +970,10 @@
         <v>12068.64</v>
       </c>
       <c r="G4">
-        <v>27548.15601071166</v>
+        <v>26210.76351071166</v>
       </c>
       <c r="H4">
-        <v>-20.74994426938493</v>
+        <v>-22.69757014055628</v>
       </c>
       <c r="I4">
         <v>43862.5</v>
@@ -984,10 +984,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>-7100.512354860971</v>
+        <v>-8941.889667360978</v>
       </c>
       <c r="C5">
-        <v>-1130.229625954827</v>
+        <v>-1634.214438454829</v>
       </c>
       <c r="D5">
         <v>153875.16</v>
@@ -999,10 +999,10 @@
         <v>12310.0128</v>
       </c>
       <c r="G5">
-        <v>30528.20782357103</v>
+        <v>28686.83051107102</v>
       </c>
       <c r="H5">
-        <v>-11.37913675955493</v>
+        <v>-13.19800061710009</v>
       </c>
       <c r="I5">
         <v>43862.5</v>
@@ -1013,10 +1013,10 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>-8178.883533237675</v>
+        <v>-10536.84527855018</v>
       </c>
       <c r="C6">
-        <v>-1078.371178376704</v>
+        <v>-1594.955611189204</v>
       </c>
       <c r="D6">
         <v>156952.6632</v>
@@ -1028,10 +1028,10 @@
         <v>12556.213056</v>
       </c>
       <c r="G6">
-        <v>33713.88387027453</v>
+        <v>31355.92212496203</v>
       </c>
       <c r="H6">
-        <v>-6.367018772471189</v>
+        <v>-8.048980462214427</v>
       </c>
       <c r="I6">
         <v>43862.5</v>
@@ -1042,10 +1042,10 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>-9200.837262046804</v>
+        <v>-12088.29805099212</v>
       </c>
       <c r="C7">
-        <v>-1021.95372880913</v>
+        <v>-1551.452772441939</v>
       </c>
       <c r="D7">
         <v>160091.716464</v>
@@ -1057,10 +1057,10 @@
         <v>12807.33731712</v>
       </c>
       <c r="G7">
-        <v>37118.08697273372</v>
+        <v>34230.6261837884</v>
       </c>
       <c r="H7">
-        <v>-3.283974572695414</v>
+        <v>-4.837839697831924</v>
       </c>
       <c r="I7">
         <v>43862.5</v>
@@ -1071,10 +1071,10 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>-10161.71406261716</v>
+        <v>-13591.91137128611</v>
       </c>
       <c r="C8">
-        <v>-960.8768005703614</v>
+        <v>-1503.613320293993</v>
       </c>
       <c r="D8">
         <v>163293.55079328</v>
@@ -1086,10 +1086,10 @@
         <v>13063.4840634624</v>
       </c>
       <c r="G8">
-        <v>40754.37519128665</v>
+        <v>37324.1778826177</v>
       </c>
       <c r="H8">
-        <v>-1.217470459994541</v>
+        <v>-2.654440658909074</v>
       </c>
       <c r="I8">
         <v>43862.5</v>
@@ -1100,10 +1100,10 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>-11056.75200761351</v>
+        <v>-15043.25424899918</v>
       </c>
       <c r="C9">
-        <v>-895.037944996343</v>
+        <v>-1451.342877713069</v>
       </c>
       <c r="D9">
         <v>166559.4218091457</v>
@@ -1115,10 +1115,10 @@
         <v>13324.75374473165</v>
       </c>
       <c r="G9">
-        <v>44637.00344936474</v>
+        <v>40650.50120797908</v>
       </c>
       <c r="H9">
-        <v>0.2503621393163291</v>
+        <v>-1.080528115622903</v>
       </c>
       <c r="I9">
         <v>43862.5</v>
@@ -1129,10 +1129,10 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>-11881.08472135204</v>
+        <v>-16437.79951877235</v>
       </c>
       <c r="C10">
-        <v>-824.3327137385313</v>
+        <v>-1394.545269773172</v>
       </c>
       <c r="D10">
         <v>169890.6102453286</v>
@@ -1144,10 +1144,10 @@
         <v>13591.24881962629</v>
       </c>
       <c r="G10">
-        <v>48780.96808141219</v>
+        <v>44224.25328399187</v>
       </c>
       <c r="H10">
-        <v>1.337370072019706</v>
+        <v>0.1027229053316869</v>
       </c>
       <c r="I10">
         <v>43862.5</v>
@@ -1158,10 +1158,10 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>-12629.73935258507</v>
+        <v>-17770.9220199409</v>
       </c>
       <c r="C11">
-        <v>-748.6546312330363</v>
+        <v>-1333.122501168541</v>
       </c>
       <c r="D11">
         <v>173288.4224502351</v>
@@ -1173,10 +1173,10 @@
         <v>13863.07379601881</v>
       </c>
       <c r="G11">
-        <v>53202.05451659196</v>
+        <v>48060.87184923614</v>
       </c>
       <c r="H11">
-        <v>2.16802602528845</v>
+        <v>1.020826690650378</v>
       </c>
       <c r="I11">
         <v>43862.5</v>
@@ -1187,10 +1187,10 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>-13297.6345199651</v>
+        <v>-19037.89675400482</v>
       </c>
       <c r="C12">
-        <v>-667.8951673800265</v>
+        <v>-1266.974734063922</v>
       </c>
       <c r="D12">
         <v>176754.1908992399</v>
@@ -1202,10 +1202,10 @@
         <v>14140.33527193919</v>
       </c>
       <c r="G12">
-        <v>57916.88832642182</v>
+        <v>52176.6260923821</v>
       </c>
       <c r="H12">
-        <v>2.818481109824966</v>
+        <v>1.750900433929381</v>
       </c>
       <c r="I12">
         <v>43862.5</v>
@@ -1216,10 +1216,10 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>-13879.57823043952</v>
+        <v>-20233.89702033023</v>
       </c>
       <c r="C13">
-        <v>-581.9437104744202</v>
+        <v>-1196.000266325413</v>
       </c>
       <c r="D13">
         <v>180289.2747172246</v>
@@ -1231,10 +1231,10 @@
         <v>14423.14197737797</v>
       </c>
       <c r="G13">
-        <v>62942.98988124645</v>
+        <v>56588.67109135574</v>
       </c>
       <c r="H13">
-        <v>3.337857574437986</v>
+        <v>2.34292580837272</v>
       </c>
       <c r="I13">
         <v>43862.5</v>
@@ -1245,10 +1245,10 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>-14370.26577087118</v>
+        <v>-21353.99253050915</v>
       </c>
       <c r="C14">
-        <v>-490.6875404316543</v>
+        <v>-1120.095510178918</v>
       </c>
       <c r="D14">
         <v>183895.0602115691</v>
@@ -1260,10 +1260,10 @@
         <v>14711.60481692553</v>
       </c>
       <c r="G14">
-        <v>68298.83287844725</v>
+        <v>61315.10611880928</v>
       </c>
       <c r="H14">
-        <v>3.759210468235108</v>
+        <v>2.830711774434014</v>
       </c>
       <c r="I14">
         <v>43862.5</v>
@@ -1274,10 +1274,10 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>-14764.27757322588</v>
+        <v>-22393.1475018548</v>
       </c>
       <c r="C15">
-        <v>-394.0118023547029</v>
+        <v>-1039.154971345654</v>
       </c>
       <c r="D15">
         <v>187572.9614158005</v>
@@ -1289,10 +1289,10 @@
         <v>15005.83691326404</v>
       </c>
       <c r="G15">
-        <v>74003.90702461201</v>
+        <v>66375.03709598308</v>
       </c>
       <c r="H15">
-        <v>4.105564560408226</v>
+        <v>3.237941909888931</v>
       </c>
       <c r="I15">
         <v>43862.5</v>
@@ -1303,10 +1303,10 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>-15056.07705371728</v>
+        <v>-23346.21873056193</v>
       </c>
       <c r="C16">
-        <v>-291.7994804914033</v>
+        <v>-953.0712287071246</v>
       </c>
       <c r="D16">
         <v>191324.4206441165</v>
@@ -1318,10 +1318,10 @@
         <v>15305.95365152932</v>
       </c>
       <c r="G16">
-        <v>80078.78517463114</v>
+        <v>71788.64349778648</v>
       </c>
       <c r="H16">
-        <v>4.393425776506388</v>
+        <v>3.581698015456847</v>
       </c>
       <c r="I16">
         <v>43862.5</v>
@@ -1332,10 +1332,10 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>-15240.008426351</v>
+        <v>-24207.95364511676</v>
       </c>
       <c r="C17">
-        <v>-183.9313726337168</v>
+        <v>-861.7349145548324</v>
       </c>
       <c r="D17">
         <v>195150.9090569989</v>
@@ -1347,10 +1347,10 @@
         <v>15612.07272455991</v>
       </c>
       <c r="G17">
-        <v>86545.19525295934</v>
+        <v>77577.25003419357</v>
       </c>
       <c r="H17">
-        <v>4.634918102108165</v>
+        <v>3.874608501554744</v>
       </c>
       <c r="I17">
         <v>43862.5</v>
@@ -1361,10 +1361,10 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>-15310.29449136486</v>
+        <v>-24972.98834059978</v>
       </c>
       <c r="C18">
-        <v>-70.28606501386366</v>
+        <v>-765.034695483012</v>
       </c>
       <c r="D18">
         <v>199053.9272381389</v>
@@ -1376,10 +1376,10 @@
         <v>15924.31417905111</v>
       </c>
       <c r="G18">
-        <v>93426.09730619227</v>
+        <v>83763.40345695734</v>
       </c>
       <c r="H18">
-        <v>4.839134419868896</v>
+        <v>4.126209329643382</v>
       </c>
       <c r="I18">
         <v>43862.5</v>
@@ -1390,10 +1390,10 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>-15261.03439912004</v>
+        <v>-25635.84559458582</v>
       </c>
       <c r="C19">
-        <v>49.2600922448255</v>
+        <v>-662.857253986046</v>
       </c>
       <c r="D19">
         <v>203035.0057829016</v>
@@ -1405,10 +1405,10 @@
         <v>16242.80046263213</v>
       </c>
       <c r="G19">
-        <v>100745.7660617837</v>
+        <v>90370.95486631793</v>
       </c>
       <c r="H19">
-        <v>5.01301860788943</v>
+        <v>4.343834760834664</v>
       </c>
       <c r="I19">
         <v>43862.5</v>
@@ -1419,10 +1419,10 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>-15086.20139005877</v>
+        <v>-26190.93286541119</v>
       </c>
       <c r="C20">
-        <v>174.8330090612689</v>
+        <v>-555.0872708253692</v>
       </c>
       <c r="D20">
         <v>207095.7058985597</v>
@@ -1434,10 +1434,10 @@
         <v>16567.65647188477</v>
       </c>
       <c r="G20">
-        <v>108529.8793952903</v>
+        <v>97425.14791993788</v>
       </c>
       <c r="H20">
-        <v>5.161957925469496</v>
+        <v>4.533217068223871</v>
       </c>
       <c r="I20">
         <v>43862.5</v>
@@ -1448,10 +1448,10 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>-14779.64051140931</v>
+        <v>-26632.54027364554</v>
       </c>
       <c r="C21">
-        <v>306.5608786494577</v>
+        <v>-441.6074082343494</v>
       </c>
       <c r="D21">
         <v>211237.6200165309</v>
@@ -1463,10 +1463,10 @@
         <v>16899.00960132247</v>
       </c>
       <c r="G21">
-        <v>116805.6131381277</v>
+        <v>104952.7133758914</v>
       </c>
       <c r="H21">
-        <v>5.290190687503293</v>
+        <v>4.698900397496364</v>
       </c>
       <c r="I21">
         <v>43862.5</v>
@@ -1477,10 +1477,10 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>-14335.06631138658</v>
+        <v>-26954.83856767871</v>
       </c>
       <c r="C22">
-        <v>444.5742000227328</v>
+        <v>-322.2982940331713</v>
       </c>
       <c r="D22">
         <v>215462.3724168615</v>
@@ -1492,10 +1492,10 @@
         <v>17236.98979334892</v>
       </c>
       <c r="G22">
-        <v>125601.7426895949</v>
+        <v>112981.9704333027</v>
       </c>
       <c r="H22">
-        <v>5.401092927579509</v>
+        <v>4.844532656409584</v>
       </c>
       <c r="I22">
         <v>43862.5</v>
@@ -1506,10 +1506,10 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>-13746.06051170903</v>
+        <v>-27151.87707440847</v>
       </c>
       <c r="C23">
-        <v>589.0057996775485</v>
+        <v>-197.0385067297576</v>
       </c>
       <c r="D23">
         <v>219771.6198651987</v>
@@ -1521,10 +1521,10 @@
         <v>17581.7295892159</v>
       </c>
       <c r="G23">
-        <v>134948.7519310397</v>
+        <v>121542.9353683402</v>
       </c>
       <c r="H23">
-        <v>5.497383856713944</v>
+        <v>4.97307539969376</v>
       </c>
       <c r="I23">
         <v>43862.5</v>
@@ -1535,10 +1535,10 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>-13006.06965932821</v>
+        <v>-27217.58163609514</v>
       </c>
       <c r="C24">
-        <v>739.9908523808208</v>
+        <v>-65.70456168666533</v>
       </c>
       <c r="D24">
         <v>224167.0522625027</v>
@@ -1550,10 +1550,10 @@
         <v>17933.36418100022</v>
       </c>
       <c r="G24">
-        <v>144878.9499766639</v>
+        <v>130667.437999897</v>
       </c>
       <c r="H24">
-        <v>5.58127565472808</v>
+        <v>5.086957381344281</v>
       </c>
       <c r="I24">
         <v>43862.5</v>
@@ -1564,10 +1564,10 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>-12108.40275834716</v>
+        <v>-27145.75253453326</v>
       </c>
       <c r="C25">
-        <v>897.6669009810466</v>
+        <v>71.82910156187609</v>
       </c>
       <c r="D25">
         <v>228650.3933077528</v>
@@ -1579,10 +1579,10 @@
         <v>18292.03146462022</v>
       </c>
       <c r="G25">
-        <v>155426.5963347945</v>
+        <v>140389.2465586084</v>
       </c>
       <c r="H25">
-        <v>5.654584364416904</v>
+        <v>5.188188656304504</v>
       </c>
       <c r="I25">
         <v>43862.5</v>
@@ -1593,10 +1593,10 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>-11046.22888318833</v>
+        <v>-26930.06240377908</v>
       </c>
       <c r="C26">
-        <v>1062.173875158829</v>
+        <v>215.690130754183</v>
       </c>
       <c r="D26">
         <v>233223.4011739078</v>
@@ -1608,10 +1608,10 @@
         <v>18657.87209391263</v>
       </c>
       <c r="G26">
-        <v>166628.0350956667</v>
+        <v>150744.201575076</v>
       </c>
       <c r="H26">
-        <v>5.718813134913003</v>
+        <v>5.278446569867845</v>
       </c>
       <c r="I26">
         <v>43862.5</v>
@@ -1622,10 +1622,10 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>-9812.574774160226</v>
+        <v>-26564.05413276573</v>
       </c>
       <c r="C27">
-        <v>1233.654109028105</v>
+        <v>366.0082710133429</v>
       </c>
       <c r="D27">
         <v>237887.869197386</v>
@@ -1637,10 +1637,10 @@
         <v>19031.02953579088</v>
       </c>
       <c r="G27">
-        <v>178521.8388070998</v>
+        <v>161770.3594484943</v>
       </c>
       <c r="H27">
-        <v>5.775215500424702</v>
+        <v>5.359141396322653</v>
       </c>
       <c r="I27">
         <v>43862.5</v>
@@ -1651,10 +1651,10 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>-8400.322416665578</v>
+        <v>-26041.13875923623</v>
       </c>
       <c r="C28">
-        <v>1412.252357494648</v>
+        <v>522.9153735295076</v>
       </c>
       <c r="D28">
         <v>242645.6265813337</v>
@@ -1666,10 +1666,10 @@
         <v>19411.6501265067</v>
       </c>
       <c r="G28">
-        <v>191148.9627481138</v>
+        <v>173508.1464055432</v>
       </c>
       <c r="H28">
-        <v>5.824844038284493</v>
+        <v>5.431467032572934</v>
       </c>
       <c r="I28">
         <v>43862.5</v>
@@ -1680,10 +1680,10 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>-6802.206605392172</v>
+        <v>-25354.59335652708</v>
       </c>
       <c r="C29">
-        <v>1598.115811273407</v>
+        <v>686.5454027091437</v>
       </c>
       <c r="D29">
         <v>247498.5391129604</v>
@@ -1695,10 +1695,10 @@
         <v>19799.88312903683</v>
       </c>
       <c r="G29">
-        <v>204552.9103627954</v>
+        <v>186000.5236116604</v>
       </c>
       <c r="H29">
-        <v>5.868588180321543</v>
+        <v>5.496440571553296</v>
       </c>
       <c r="I29">
         <v>43862.5</v>
@@ -1709,10 +1709,10 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>-5010.812494930962</v>
+        <v>-24497.55891484424</v>
       </c>
       <c r="C30">
-        <v>1791.394110461209</v>
+        <v>857.034441682843</v>
       </c>
       <c r="D30">
         <v>252448.5098952196</v>
@@ -1724,10 +1724,10 @@
         <v>20195.88079161757</v>
       </c>
       <c r="G30">
-        <v>218779.910672823</v>
+        <v>199293.1642529097</v>
       </c>
       <c r="H30">
-        <v>5.907203881263756</v>
+        <v>5.554933501053871</v>
       </c>
       <c r="I30">
         <v>43862.5</v>
@@ -1738,10 +1738,10 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>-3018.573138375094</v>
+        <v>-23463.0382187862</v>
       </c>
       <c r="C31">
-        <v>1992.239356555868</v>
+        <v>1034.520696058036</v>
       </c>
       <c r="D31">
         <v>257497.480093124</v>
@@ -1753,10 +1753,10 @@
         <v>20599.79840744992</v>
       </c>
       <c r="G31">
-        <v>233879.108547302</v>
+        <v>213434.6434668908</v>
       </c>
       <c r="H31">
-        <v>5.941337106727618</v>
+        <v>5.60769652521993</v>
       </c>
       <c r="I31">
         <v>43862.5</v>
